--- a/reductions-lit/data/lit_dat.xlsx
+++ b/reductions-lit/data/lit_dat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions-lit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D484913B-73F5-43B3-A6A4-9D9DF7B62CB7}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40461209-7FEB-4794-8967-57D2A0E2342A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
   </bookViews>
@@ -4828,7 +4828,8 @@
     <col min="22" max="22" width="7.5703125" style="1" customWidth="1"/>
     <col min="23" max="23" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="10.5703125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="19.140625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" customWidth="1"/>
     <col min="27" max="28" width="9.42578125" style="2" customWidth="1"/>
     <col min="29" max="29" width="20.42578125" style="2" customWidth="1"/>
     <col min="30" max="31" width="44.5703125" style="1" customWidth="1"/>
@@ -23993,7 +23994,7 @@
         <v>0.17</v>
       </c>
       <c r="V137" s="1">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="W137" s="2">
         <v>35</v>
@@ -24134,7 +24135,7 @@
         <v>0.1</v>
       </c>
       <c r="V138" s="1">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="W138" s="2">
         <v>35</v>
@@ -24275,7 +24276,7 @@
         <v>0.2</v>
       </c>
       <c r="V139" s="1">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="W139" s="2">
         <v>35</v>
@@ -24416,7 +24417,7 @@
         <v>0.15</v>
       </c>
       <c r="V140" s="1">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="W140" s="2">
         <v>35</v>
@@ -24557,7 +24558,7 @@
         <v>0.03</v>
       </c>
       <c r="V141" s="1">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W141" s="2">
         <v>35</v>
@@ -24698,7 +24699,7 @@
         <v>0.03</v>
       </c>
       <c r="V142" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W142" s="2">
         <v>35</v>
@@ -24839,7 +24840,7 @@
         <v>0.13</v>
       </c>
       <c r="V143" s="1">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="W143" s="2">
         <v>35</v>
@@ -24980,7 +24981,7 @@
         <v>0.03</v>
       </c>
       <c r="V144" s="8">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="W144" s="11">
         <v>35</v>
@@ -44482,7 +44483,7 @@
       <c r="T281" s="1"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="X281" s="2">
         <v>84.8</v>
@@ -44697,7 +44698,7 @@
       <c r="T283"/>
       <c r="U283"/>
       <c r="V283" s="1">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="W283"/>
       <c r="X283" s="2">

--- a/reductions-lit/data/lit_dat.xlsx
+++ b/reductions-lit/data/lit_dat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions-lit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F36D651-0899-492C-9B00-3B8C83774087}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="8_{7C4171F8-D199-4843-B714-C3F258BC4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7EB1E2B-69FE-42B0-9804-D589A5348985}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{DF353E34-80BC-440D-84E6-1A1BEACE8767}"/>
   </bookViews>
@@ -301,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="1051">
   <si>
     <t>Study</t>
   </si>
@@ -3466,9 +3466,6 @@
   </si>
   <si>
     <t>SSD</t>
-  </si>
-  <si>
-    <t>Wagner et al. 2021</t>
   </si>
   <si>
     <t>Wagner, C., T. Nyord, A.V. Vestergaard, S.D. Hafner, A.S. Pacholski. 2021. Acidification effects on in situ ammonia emissions and cereal yields depending on slurry type and application method. doi.org/10.3390/agriculture11111053</t>
@@ -5091,7 +5088,7 @@
         <v>100</v>
       </c>
       <c r="AE2" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>99</v>
@@ -5239,7 +5236,7 @@
         <v>100</v>
       </c>
       <c r="AE3" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>99</v>
@@ -5683,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="AE6" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF6" s="2" t="s">
         <v>99</v>
@@ -5825,7 +5822,7 @@
         <v>100</v>
       </c>
       <c r="AE7" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>99</v>
@@ -6261,7 +6258,7 @@
         <v>100</v>
       </c>
       <c r="AE10" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF10" s="2" t="s">
         <v>99</v>
@@ -6403,7 +6400,7 @@
         <v>100</v>
       </c>
       <c r="AE11" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF11" s="2" t="s">
         <v>99</v>
@@ -6693,7 +6690,7 @@
         <v>100</v>
       </c>
       <c r="AE13" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF13" s="2" t="s">
         <v>99</v>
@@ -7530,7 +7527,7 @@
         <v>187</v>
       </c>
       <c r="AE19" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF19" s="2" t="s">
         <v>189</v>
@@ -7944,7 +7941,7 @@
         <v>187</v>
       </c>
       <c r="AE22" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF22" s="2" t="s">
         <v>189</v>
@@ -8351,7 +8348,7 @@
         <v>187</v>
       </c>
       <c r="AE25" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF25" s="2" t="s">
         <v>189</v>
@@ -8622,7 +8619,7 @@
         <v>187</v>
       </c>
       <c r="AE27" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF27" s="2" t="s">
         <v>189</v>
@@ -11210,7 +11207,7 @@
         <v>305</v>
       </c>
       <c r="AE47" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF47" s="1" t="s">
         <v>303</v>
@@ -11346,7 +11343,7 @@
         <v>304</v>
       </c>
       <c r="AE48" s="49" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF48" s="8" t="s">
         <v>303</v>
@@ -14528,7 +14525,7 @@
         <v>386</v>
       </c>
       <c r="AE71" s="26" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>383</v>
@@ -14815,7 +14812,7 @@
         <v>395</v>
       </c>
       <c r="AE73" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF73" s="2" t="s">
         <v>394</v>
@@ -14958,7 +14955,7 @@
         <v>395</v>
       </c>
       <c r="AE74" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF74" s="2" t="s">
         <v>394</v>
@@ -15101,7 +15098,7 @@
         <v>395</v>
       </c>
       <c r="AE75" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF75" s="11" t="s">
         <v>394</v>
@@ -16481,7 +16478,7 @@
         <v>440</v>
       </c>
       <c r="AE85" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF85" s="2" t="s">
         <v>439</v>
@@ -16773,7 +16770,7 @@
         <v>442</v>
       </c>
       <c r="AE87" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF87" s="2" t="s">
         <v>439</v>
@@ -16919,7 +16916,7 @@
         <v>440</v>
       </c>
       <c r="AE88" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF88" s="2" t="s">
         <v>439</v>
@@ -17213,7 +17210,7 @@
         <v>442</v>
       </c>
       <c r="AE90" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF90" s="2" t="s">
         <v>439</v>
@@ -17359,7 +17356,7 @@
         <v>440</v>
       </c>
       <c r="AE91" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF91" s="2" t="s">
         <v>439</v>
@@ -17653,7 +17650,7 @@
         <v>442</v>
       </c>
       <c r="AE93" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF93" s="2" t="s">
         <v>439</v>
@@ -17800,7 +17797,7 @@
         <v>440</v>
       </c>
       <c r="AE94" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF94" s="2" t="s">
         <v>439</v>
@@ -18094,7 +18091,7 @@
         <v>442</v>
       </c>
       <c r="AE96" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF96" s="2" t="s">
         <v>439</v>
@@ -18241,7 +18238,7 @@
         <v>440</v>
       </c>
       <c r="AE97" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF97" s="2" t="s">
         <v>439</v>
@@ -18535,7 +18532,7 @@
         <v>442</v>
       </c>
       <c r="AE99" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF99" s="2" t="s">
         <v>439</v>
@@ -18682,7 +18679,7 @@
         <v>440</v>
       </c>
       <c r="AE100" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF100" s="2" t="s">
         <v>439</v>
@@ -18976,7 +18973,7 @@
         <v>442</v>
       </c>
       <c r="AE102" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF102" s="2" t="s">
         <v>439</v>
@@ -19123,7 +19120,7 @@
         <v>440</v>
       </c>
       <c r="AE103" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF103" s="2" t="s">
         <v>439</v>
@@ -19417,7 +19414,7 @@
         <v>442</v>
       </c>
       <c r="AE105" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF105" s="2" t="s">
         <v>439</v>
@@ -19564,7 +19561,7 @@
         <v>440</v>
       </c>
       <c r="AE106" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF106" s="2" t="s">
         <v>439</v>
@@ -19859,7 +19856,7 @@
         <v>442</v>
       </c>
       <c r="AE108" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF108" s="11" t="s">
         <v>439</v>
@@ -20651,7 +20648,7 @@
         <v>31</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>488</v>
@@ -20731,7 +20728,7 @@
         <v>499</v>
       </c>
       <c r="AE114" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF114" s="25" t="s">
         <v>500</v>
@@ -20790,7 +20787,7 @@
         <v>31</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>488</v>
@@ -20931,7 +20928,7 @@
         <v>31</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>488</v>
@@ -21011,7 +21008,7 @@
         <v>499</v>
       </c>
       <c r="AE116" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF116" s="2" t="s">
         <v>500</v>
@@ -21070,7 +21067,7 @@
         <v>31</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>488</v>
@@ -21211,7 +21208,7 @@
         <v>31</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>488</v>
@@ -21291,7 +21288,7 @@
         <v>499</v>
       </c>
       <c r="AE118" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF118" s="2" t="s">
         <v>500</v>
@@ -21352,7 +21349,7 @@
         <v>31</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>488</v>
@@ -28280,7 +28277,7 @@
         <v>619</v>
       </c>
       <c r="AE167" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF167" s="2" t="s">
         <v>617</v>
@@ -28562,7 +28559,7 @@
         <v>619</v>
       </c>
       <c r="AE169" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF169" s="2" t="s">
         <v>617</v>
@@ -28844,7 +28841,7 @@
         <v>619</v>
       </c>
       <c r="AE171" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF171" s="2" t="s">
         <v>617</v>
@@ -29126,7 +29123,7 @@
         <v>619</v>
       </c>
       <c r="AE173" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF173" s="11" t="s">
         <v>617</v>
@@ -30368,7 +30365,7 @@
         <v>667</v>
       </c>
       <c r="AE182" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF182" s="2" t="s">
         <v>666</v>
@@ -30515,7 +30512,7 @@
         <v>667</v>
       </c>
       <c r="AE183" s="49" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF183" s="11" t="s">
         <v>666</v>
@@ -31634,7 +31631,7 @@
         <v>692</v>
       </c>
       <c r="AE191" s="47" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF191" s="2" t="s">
         <v>694</v>
@@ -32057,7 +32054,7 @@
         <v>705</v>
       </c>
       <c r="AE194" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF194" s="2" t="s">
         <v>709</v>
@@ -32200,7 +32197,7 @@
         <v>706</v>
       </c>
       <c r="AE195" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF195" s="2" t="s">
         <v>709</v>
@@ -32623,7 +32620,7 @@
         <v>705</v>
       </c>
       <c r="AE198" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF198" s="2" t="s">
         <v>709</v>
@@ -32764,7 +32761,7 @@
         <v>706</v>
       </c>
       <c r="AE199" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF199" s="2" t="s">
         <v>709</v>
@@ -33189,7 +33186,7 @@
         <v>722</v>
       </c>
       <c r="AE202" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF202" s="2" t="s">
         <v>721</v>
@@ -33474,7 +33471,7 @@
         <v>722</v>
       </c>
       <c r="AE204" s="47" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF204" s="2" t="s">
         <v>721</v>
@@ -33754,7 +33751,7 @@
         <v>723</v>
       </c>
       <c r="AE206" s="26" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AF206" s="1" t="s">
         <v>724</v>
@@ -33816,7 +33813,7 @@
         <v>47</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>731</v>
@@ -33957,7 +33954,7 @@
         <v>47</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>731</v>
@@ -34098,7 +34095,7 @@
         <v>47</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>731</v>
@@ -34239,7 +34236,7 @@
         <v>48</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>743</v>
@@ -34388,7 +34385,7 @@
         <v>48</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C211" s="23" t="s">
         <v>743</v>
@@ -34536,7 +34533,7 @@
         <v>48</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>743</v>
@@ -34683,7 +34680,7 @@
         <v>48</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>743</v>
@@ -36646,7 +36643,7 @@
         <v>825</v>
       </c>
       <c r="AE226" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF226" s="2" t="s">
         <v>822</v>
@@ -36794,7 +36791,7 @@
         <v>826</v>
       </c>
       <c r="AE227" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF227" s="2" t="s">
         <v>822</v>
@@ -37090,7 +37087,7 @@
         <v>830</v>
       </c>
       <c r="AE229" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF229" s="2" t="s">
         <v>828</v>
@@ -37238,7 +37235,7 @@
         <v>831</v>
       </c>
       <c r="AE230" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF230" s="2" t="s">
         <v>828</v>
@@ -37538,7 +37535,7 @@
         <v>825</v>
       </c>
       <c r="AE232" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF232" s="2" t="s">
         <v>822</v>
@@ -37688,7 +37685,7 @@
         <v>826</v>
       </c>
       <c r="AE233" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF233" s="2" t="s">
         <v>822</v>
@@ -37989,7 +37986,7 @@
         <v>830</v>
       </c>
       <c r="AE235" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF235" s="2" t="s">
         <v>828</v>
@@ -38140,7 +38137,7 @@
         <v>831</v>
       </c>
       <c r="AE236" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF236" s="2" t="s">
         <v>828</v>
@@ -38439,7 +38436,7 @@
         <v>825</v>
       </c>
       <c r="AE238" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF238" s="2" t="s">
         <v>822</v>
@@ -38588,7 +38585,7 @@
         <v>826</v>
       </c>
       <c r="AE239" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF239" s="2" t="s">
         <v>822</v>
@@ -38886,7 +38883,7 @@
         <v>830</v>
       </c>
       <c r="AE241" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF241" s="2" t="s">
         <v>828</v>
@@ -39035,7 +39032,7 @@
         <v>831</v>
       </c>
       <c r="AE242" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF242" s="2" t="s">
         <v>828</v>
@@ -39334,7 +39331,7 @@
         <v>825</v>
       </c>
       <c r="AE244" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF244" s="2" t="s">
         <v>822</v>
@@ -39484,7 +39481,7 @@
         <v>826</v>
       </c>
       <c r="AE245" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF245" s="2" t="s">
         <v>822</v>
@@ -39782,7 +39779,7 @@
         <v>825</v>
       </c>
       <c r="AE247" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF247" s="2" t="s">
         <v>822</v>
@@ -39932,7 +39929,7 @@
         <v>826</v>
       </c>
       <c r="AE248" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF248" s="2" t="s">
         <v>822</v>
@@ -40230,7 +40227,7 @@
         <v>830</v>
       </c>
       <c r="AE250" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF250" s="2" t="s">
         <v>828</v>
@@ -40379,7 +40376,7 @@
         <v>831</v>
       </c>
       <c r="AE251" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF251" s="2" t="s">
         <v>828</v>
@@ -40676,7 +40673,7 @@
         <v>825</v>
       </c>
       <c r="AE253" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF253" s="2" t="s">
         <v>822</v>
@@ -40825,7 +40822,7 @@
         <v>826</v>
       </c>
       <c r="AE254" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF254" s="2" t="s">
         <v>822</v>
@@ -41124,7 +41121,7 @@
         <v>830</v>
       </c>
       <c r="AE256" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF256" s="2" t="s">
         <v>828</v>
@@ -41274,7 +41271,7 @@
         <v>831</v>
       </c>
       <c r="AE257" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF257" s="2" t="s">
         <v>828</v>
@@ -41576,7 +41573,7 @@
         <v>825</v>
       </c>
       <c r="AE259" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF259" s="2" t="s">
         <v>822</v>
@@ -41726,7 +41723,7 @@
         <v>826</v>
       </c>
       <c r="AE260" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF260" s="2" t="s">
         <v>822</v>
@@ -42028,7 +42025,7 @@
         <v>830</v>
       </c>
       <c r="AE262" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF262" s="2" t="s">
         <v>828</v>
@@ -42179,7 +42176,7 @@
         <v>831</v>
       </c>
       <c r="AE263" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF263" s="2" t="s">
         <v>828</v>
@@ -42481,7 +42478,7 @@
         <v>825</v>
       </c>
       <c r="AE265" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF265" s="2" t="s">
         <v>822</v>
@@ -42632,7 +42629,7 @@
         <v>826</v>
       </c>
       <c r="AE266" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF266" s="2" t="s">
         <v>822</v>
@@ -42932,7 +42929,7 @@
         <v>830</v>
       </c>
       <c r="AE268" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF268" s="2" t="s">
         <v>828</v>
@@ -43083,7 +43080,7 @@
         <v>831</v>
       </c>
       <c r="AE269" s="47" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AF269" s="11" t="s">
         <v>828</v>
@@ -44129,7 +44126,7 @@
         <v>57</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>978</v>
+        <v>1049</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>979</v>
@@ -44229,7 +44226,7 @@
         <v>57</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>978</v>
+        <v>1049</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>979</v>
@@ -44329,10 +44326,10 @@
         <v>58</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>489</v>
@@ -44356,7 +44353,7 @@
         <v>2014</v>
       </c>
       <c r="M280" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N280" s="2" t="s">
         <v>882</v>
@@ -44393,10 +44390,10 @@
         <v>894</v>
       </c>
       <c r="AD280" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="AE280" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="AE280" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="AF280" s="2" t="s">
         <v>923</v>
@@ -44435,10 +44432,10 @@
         <v>58</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>489</v>
@@ -44462,7 +44459,7 @@
         <v>2014</v>
       </c>
       <c r="M281" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N281" s="2" t="s">
         <v>882</v>
@@ -44499,7 +44496,7 @@
         <v>894</v>
       </c>
       <c r="AD281" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AE281" s="1"/>
       <c r="AF281" s="2" t="s">
@@ -44509,7 +44506,7 @@
         <v>933</v>
       </c>
       <c r="AH281" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AI281" s="2" t="s">
         <v>921</v>
@@ -44542,10 +44539,10 @@
         <v>58</v>
       </c>
       <c r="B282" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C282" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>489</v>
@@ -44569,7 +44566,7 @@
         <v>2014</v>
       </c>
       <c r="M282" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N282" s="2" t="s">
         <v>882</v>
@@ -44648,10 +44645,10 @@
         <v>58</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>489</v>
@@ -44677,7 +44674,7 @@
         <v>2014</v>
       </c>
       <c r="M283" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N283" s="2" t="s">
         <v>882</v>
@@ -44716,19 +44713,19 @@
         <v>894</v>
       </c>
       <c r="AD283" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE283" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF283" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG283" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH283" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI283" s="2" t="s">
         <v>921</v>
@@ -44760,10 +44757,10 @@
         <v>58</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>489</v>
@@ -44828,19 +44825,19 @@
         <v>894</v>
       </c>
       <c r="AD284" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE284" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF284" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG284" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH284" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI284" s="2" t="s">
         <v>921</v>
@@ -44870,10 +44867,10 @@
         <v>58</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>489</v>
@@ -44905,7 +44902,7 @@
         <v>882</v>
       </c>
       <c r="O285" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="P285" s="2" t="s">
         <v>533</v>
@@ -44938,13 +44935,13 @@
         <v>894</v>
       </c>
       <c r="AD285" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE285" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF285" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG285" s="2" t="s">
         <v>933</v>
@@ -44980,10 +44977,10 @@
         <v>58</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>489</v>
@@ -45015,10 +45012,10 @@
         <v>882</v>
       </c>
       <c r="O286" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="P286" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="P286" s="2" t="s">
-        <v>999</v>
       </c>
       <c r="Q286" s="1" t="s">
         <v>93</v>
@@ -45048,19 +45045,19 @@
         <v>894</v>
       </c>
       <c r="AD286" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE286" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF286" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG286" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH286" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI286" s="2" t="s">
         <v>921</v>
@@ -45090,10 +45087,10 @@
         <v>58</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>489</v>
@@ -45125,7 +45122,7 @@
         <v>882</v>
       </c>
       <c r="O287" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P287" s="2" t="s">
         <v>886</v>
@@ -45158,19 +45155,19 @@
         <v>894</v>
       </c>
       <c r="AD287" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE287" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF287" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG287" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH287" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI287" s="2" t="s">
         <v>921</v>
@@ -45200,10 +45197,10 @@
         <v>58</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>489</v>
@@ -45235,7 +45232,7 @@
         <v>882</v>
       </c>
       <c r="O288" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="P288" s="2" t="s">
         <v>533</v>
@@ -45268,19 +45265,19 @@
         <v>894</v>
       </c>
       <c r="AD288" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE288" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF288" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG288" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH288" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AI288" s="2" t="s">
         <v>921</v>
@@ -45309,10 +45306,10 @@
         <v>58</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>489</v>
@@ -45377,19 +45374,19 @@
         <v>894</v>
       </c>
       <c r="AD289" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE289" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF289" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG289" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH289" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI289" s="2" t="s">
         <v>921</v>
@@ -45418,10 +45415,10 @@
         <v>58</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>489</v>
@@ -45453,7 +45450,7 @@
         <v>882</v>
       </c>
       <c r="O290" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="P290" s="2" t="s">
         <v>533</v>
@@ -45486,13 +45483,13 @@
         <v>894</v>
       </c>
       <c r="AD290" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE290" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF290" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG290" s="2" t="s">
         <v>933</v>
@@ -45527,10 +45524,10 @@
         <v>58</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>489</v>
@@ -45562,10 +45559,10 @@
         <v>882</v>
       </c>
       <c r="O291" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="P291" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="P291" s="2" t="s">
-        <v>999</v>
       </c>
       <c r="Q291" s="1" t="s">
         <v>93</v>
@@ -45595,19 +45592,19 @@
         <v>894</v>
       </c>
       <c r="AD291" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE291" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF291" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG291" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH291" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI291" s="2" t="s">
         <v>921</v>
@@ -45636,10 +45633,10 @@
         <v>58</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>489</v>
@@ -45671,7 +45668,7 @@
         <v>882</v>
       </c>
       <c r="O292" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P292" s="2" t="s">
         <v>886</v>
@@ -45704,19 +45701,19 @@
         <v>894</v>
       </c>
       <c r="AD292" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE292" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF292" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG292" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH292" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI292" s="2" t="s">
         <v>921</v>
@@ -45745,10 +45742,10 @@
         <v>58</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>489</v>
@@ -45780,7 +45777,7 @@
         <v>882</v>
       </c>
       <c r="O293" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="P293" s="2" t="s">
         <v>533</v>
@@ -45813,19 +45810,19 @@
         <v>894</v>
       </c>
       <c r="AD293" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AE293" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF293" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AG293" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH293" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AI293" s="2" t="s">
         <v>921</v>
@@ -45854,10 +45851,10 @@
         <v>59</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>489</v>
@@ -45877,7 +45874,7 @@
         <v>2012</v>
       </c>
       <c r="M294" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N294" s="2" t="s">
         <v>883</v>
@@ -45898,7 +45895,7 @@
       <c r="AB294"/>
       <c r="AC294"/>
       <c r="AD294" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AE294" s="1" t="s">
         <v>930</v>
@@ -45935,10 +45932,10 @@
         <v>59</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>489</v>
@@ -45958,7 +45955,7 @@
         <v>2012</v>
       </c>
       <c r="M295" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N295" s="2" t="s">
         <v>883</v>
@@ -45979,7 +45976,7 @@
       <c r="AB295"/>
       <c r="AC295"/>
       <c r="AD295" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AE295" s="1" t="s">
         <v>930</v>
@@ -46016,10 +46013,10 @@
         <v>59</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>489</v>
@@ -46039,7 +46036,7 @@
         <v>2012</v>
       </c>
       <c r="M296" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N296" s="2" t="s">
         <v>883</v>
@@ -46072,7 +46069,7 @@
         <v>933</v>
       </c>
       <c r="AH296" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AI296" s="2" t="s">
         <v>921</v>
@@ -46097,10 +46094,10 @@
         <v>59</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>489</v>
@@ -46120,7 +46117,7 @@
         <v>2012</v>
       </c>
       <c r="M297" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N297" s="2" t="s">
         <v>883</v>
@@ -46153,7 +46150,7 @@
         <v>933</v>
       </c>
       <c r="AH297" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AI297" s="2" t="s">
         <v>921</v>
@@ -46178,10 +46175,10 @@
         <v>59</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>489</v>
@@ -46201,7 +46198,7 @@
         <v>2012</v>
       </c>
       <c r="M298" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N298" s="2" t="s">
         <v>883</v>
@@ -46222,7 +46219,7 @@
       <c r="AB298"/>
       <c r="AC298"/>
       <c r="AD298" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AE298" s="1" t="s">
         <v>930</v>
@@ -46259,10 +46256,10 @@
         <v>59</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>489</v>
@@ -46282,7 +46279,7 @@
         <v>2012</v>
       </c>
       <c r="M299" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N299" s="2" t="s">
         <v>883</v>
@@ -46303,7 +46300,7 @@
       <c r="AB299"/>
       <c r="AC299"/>
       <c r="AD299" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AE299" s="1" t="s">
         <v>930</v>
@@ -46340,10 +46337,10 @@
         <v>59</v>
       </c>
       <c r="B300" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C300" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>489</v>
@@ -46363,7 +46360,7 @@
         <v>2012</v>
       </c>
       <c r="M300" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N300" s="2" t="s">
         <v>883</v>
@@ -46396,7 +46393,7 @@
         <v>933</v>
       </c>
       <c r="AH300" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AI300" s="2" t="s">
         <v>921</v>
@@ -46421,10 +46418,10 @@
         <v>59</v>
       </c>
       <c r="B301" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C301" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>489</v>
@@ -46444,7 +46441,7 @@
         <v>2012</v>
       </c>
       <c r="M301" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N301" s="2" t="s">
         <v>883</v>
@@ -46477,7 +46474,7 @@
         <v>933</v>
       </c>
       <c r="AH301" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AI301" s="2" t="s">
         <v>921</v>
@@ -46502,10 +46499,10 @@
         <v>59</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>489</v>
@@ -46525,7 +46522,7 @@
         <v>2013</v>
       </c>
       <c r="M302" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N302" s="2" t="s">
         <v>883</v>
@@ -46546,7 +46543,7 @@
       <c r="AB302"/>
       <c r="AC302"/>
       <c r="AD302" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AE302" s="1" t="s">
         <v>930</v>
@@ -46583,10 +46580,10 @@
         <v>59</v>
       </c>
       <c r="B303" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>489</v>
@@ -46606,7 +46603,7 @@
         <v>2013</v>
       </c>
       <c r="M303" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N303" s="2" t="s">
         <v>883</v>
@@ -46627,7 +46624,7 @@
       <c r="AB303"/>
       <c r="AC303"/>
       <c r="AD303" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AE303" s="1" t="s">
         <v>930</v>
@@ -46664,10 +46661,10 @@
         <v>59</v>
       </c>
       <c r="B304" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C304" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>489</v>
@@ -46687,7 +46684,7 @@
         <v>2013</v>
       </c>
       <c r="M304" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N304" s="2" t="s">
         <v>883</v>
@@ -46720,7 +46717,7 @@
         <v>933</v>
       </c>
       <c r="AH304" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AI304" s="2" t="s">
         <v>921</v>
@@ -46745,10 +46742,10 @@
         <v>59</v>
       </c>
       <c r="B305" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C305" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>489</v>
@@ -46768,7 +46765,7 @@
         <v>2013</v>
       </c>
       <c r="M305" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N305" s="2" t="s">
         <v>883</v>
@@ -46801,7 +46798,7 @@
         <v>933</v>
       </c>
       <c r="AH305" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AI305" s="2" t="s">
         <v>921</v>
@@ -46826,10 +46823,10 @@
         <v>59</v>
       </c>
       <c r="B306" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C306" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>489</v>
@@ -46849,7 +46846,7 @@
         <v>2013</v>
       </c>
       <c r="M306" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N306" s="2" t="s">
         <v>883</v>
@@ -46870,7 +46867,7 @@
       <c r="AB306"/>
       <c r="AC306"/>
       <c r="AD306" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AE306" s="1" t="s">
         <v>930</v>
@@ -46907,10 +46904,10 @@
         <v>59</v>
       </c>
       <c r="B307" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>489</v>
@@ -46930,7 +46927,7 @@
         <v>2013</v>
       </c>
       <c r="M307" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N307" s="2" t="s">
         <v>883</v>
@@ -46951,7 +46948,7 @@
       <c r="AB307"/>
       <c r="AC307"/>
       <c r="AD307" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AE307" s="1" t="s">
         <v>930</v>
@@ -46988,10 +46985,10 @@
         <v>59</v>
       </c>
       <c r="B308" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>489</v>
@@ -47011,7 +47008,7 @@
         <v>2013</v>
       </c>
       <c r="M308" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N308" s="2" t="s">
         <v>883</v>
@@ -47044,7 +47041,7 @@
         <v>933</v>
       </c>
       <c r="AH308" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AI308" s="2" t="s">
         <v>921</v>
@@ -47069,10 +47066,10 @@
         <v>59</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>1006</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>489</v>
@@ -47092,7 +47089,7 @@
         <v>2013</v>
       </c>
       <c r="M309" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N309" s="2" t="s">
         <v>883</v>
@@ -47125,7 +47122,7 @@
         <v>933</v>
       </c>
       <c r="AH309" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AI309" s="2" t="s">
         <v>921</v>
@@ -47150,10 +47147,10 @@
         <v>60</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>1012</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>1013</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>489</v>
@@ -47173,19 +47170,19 @@
         <v>2003</v>
       </c>
       <c r="M310" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="N310" s="2" t="s">
         <v>882</v>
       </c>
       <c r="O310" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P310" s="2" t="s">
         <v>886</v>
       </c>
       <c r="Q310" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R310" s="1">
         <v>4.2</v>
@@ -47208,7 +47205,7 @@
       <c r="Z310"/>
       <c r="AA310"/>
       <c r="AB310" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AC310"/>
       <c r="AD310" s="1" t="s">
@@ -47224,7 +47221,7 @@
         <v>933</v>
       </c>
       <c r="AH310" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI310" s="2" t="s">
         <v>921</v>
@@ -47253,19 +47250,19 @@
         <v>61</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E311" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F311" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G311"/>
       <c r="H311" s="2">
@@ -47284,13 +47281,13 @@
         <v>2019</v>
       </c>
       <c r="M311" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N311" s="2" t="s">
         <v>883</v>
       </c>
       <c r="O311" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P311" s="2" t="s">
         <v>533</v>
@@ -47321,13 +47318,13 @@
       </c>
       <c r="AC311"/>
       <c r="AD311" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AE311" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF311" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG311" s="2" t="s">
         <v>933</v>
@@ -47364,19 +47361,19 @@
         <v>61</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E312" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F312" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G312"/>
       <c r="H312" s="2">
@@ -47395,13 +47392,13 @@
         <v>2019</v>
       </c>
       <c r="M312" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N312" s="2" t="s">
         <v>883</v>
       </c>
       <c r="O312" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P312" s="2" t="s">
         <v>533</v>
@@ -47432,13 +47429,13 @@
       </c>
       <c r="AC312"/>
       <c r="AD312" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AE312" s="1" t="s">
         <v>937</v>
       </c>
       <c r="AF312" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG312" s="2" t="s">
         <v>933</v>
@@ -47469,19 +47466,19 @@
         <v>61</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E313" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F313" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G313"/>
       <c r="H313" s="2">
@@ -47500,7 +47497,7 @@
         <v>2019</v>
       </c>
       <c r="M313" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N313" s="2" t="s">
         <v>883</v>
@@ -47512,7 +47509,7 @@
         <v>533</v>
       </c>
       <c r="Q313" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R313" s="1">
         <v>9.5</v>
@@ -47537,13 +47534,13 @@
       </c>
       <c r="AC313"/>
       <c r="AD313" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AE313" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF313" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG313" s="2" t="s">
         <v>933</v>
@@ -47580,19 +47577,19 @@
         <v>61</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E314" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F314" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G314"/>
       <c r="H314" s="2">
@@ -47611,7 +47608,7 @@
         <v>2019</v>
       </c>
       <c r="M314" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N314" s="2" t="s">
         <v>883</v>
@@ -47623,7 +47620,7 @@
         <v>533</v>
       </c>
       <c r="Q314" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R314" s="1">
         <v>10.5</v>
@@ -47648,13 +47645,13 @@
       </c>
       <c r="AC314"/>
       <c r="AD314" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AE314" s="1" t="s">
         <v>937</v>
       </c>
       <c r="AF314" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG314" s="2" t="s">
         <v>933</v>
@@ -47685,19 +47682,19 @@
         <v>61</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E315" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F315" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G315"/>
       <c r="H315" s="2">
@@ -47716,7 +47713,7 @@
         <v>2019</v>
       </c>
       <c r="M315" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N315" s="2" t="s">
         <v>883</v>
@@ -47753,13 +47750,13 @@
       </c>
       <c r="AC315"/>
       <c r="AD315" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AE315" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF315" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG315" s="2" t="s">
         <v>933</v>
@@ -47796,19 +47793,19 @@
         <v>61</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E316" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G316"/>
       <c r="H316" s="2">
@@ -47827,7 +47824,7 @@
         <v>2019</v>
       </c>
       <c r="M316" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N316" s="2" t="s">
         <v>883</v>
@@ -47864,13 +47861,13 @@
       </c>
       <c r="AC316"/>
       <c r="AD316" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AE316" s="1" t="s">
         <v>937</v>
       </c>
       <c r="AF316" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG316" s="2" t="s">
         <v>933</v>
@@ -47901,19 +47898,19 @@
         <v>61</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E317" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F317" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G317"/>
       <c r="H317" s="2">
@@ -47932,7 +47929,7 @@
         <v>2019</v>
       </c>
       <c r="M317" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N317" s="2" t="s">
         <v>883</v>
@@ -47969,22 +47966,22 @@
       </c>
       <c r="AC317"/>
       <c r="AD317" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AE317" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF317" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG317" s="2" t="s">
         <v>933</v>
       </c>
       <c r="AH317" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AI317" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AJ317"/>
       <c r="AK317"/>
@@ -48010,19 +48007,19 @@
         <v>61</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E318" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G318"/>
       <c r="H318" s="2">
@@ -48041,7 +48038,7 @@
         <v>2019</v>
       </c>
       <c r="M318" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N318" s="2" t="s">
         <v>883</v>
@@ -48078,13 +48075,13 @@
       </c>
       <c r="AC318"/>
       <c r="AD318" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AE318" s="1" t="s">
         <v>933</v>
       </c>
       <c r="AF318" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG318" s="2" t="s">
         <v>933</v>
@@ -48119,19 +48116,19 @@
         <v>61</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E319" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G319"/>
       <c r="H319" s="2">
@@ -48150,13 +48147,13 @@
         <v>2019</v>
       </c>
       <c r="M319" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N319" s="2" t="s">
         <v>882</v>
       </c>
       <c r="O319" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P319" s="2" t="s">
         <v>533</v>
@@ -48190,10 +48187,10 @@
         <v>930</v>
       </c>
       <c r="AE319" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF319" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG319" s="2" t="s">
         <v>933</v>
@@ -48224,19 +48221,19 @@
         <v>61</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>530</v>
       </c>
       <c r="E320" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F320" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>1019</v>
       </c>
       <c r="G320"/>
       <c r="H320" s="2">
@@ -48255,13 +48252,13 @@
         <v>2019</v>
       </c>
       <c r="M320" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N320" s="2" t="s">
         <v>882</v>
       </c>
       <c r="O320" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P320" s="2" t="s">
         <v>533</v>
@@ -48295,10 +48292,10 @@
         <v>930</v>
       </c>
       <c r="AE320" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AF320" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AG320" s="2" t="s">
         <v>933</v>
@@ -48329,13 +48326,13 @@
         <v>62</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D321" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="D321" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="P321" s="2" t="s">
         <v>533</v>
@@ -48364,13 +48361,13 @@
         <v>62</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P322" s="2" t="s">
         <v>533</v>
@@ -48399,13 +48396,13 @@
         <v>62</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P323" s="2" t="s">
         <v>533</v>
@@ -48434,13 +48431,13 @@
         <v>62</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P324" s="2" t="s">
         <v>533</v>
@@ -48469,13 +48466,13 @@
         <v>62</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P325" s="2" t="s">
         <v>533</v>
@@ -48504,13 +48501,13 @@
         <v>62</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P326" s="2" t="s">
         <v>533</v>
@@ -48539,13 +48536,13 @@
         <v>62</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P327" s="2" t="s">
         <v>533</v>
@@ -48574,13 +48571,13 @@
         <v>62</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P328" s="2" t="s">
         <v>533</v>
@@ -48609,13 +48606,13 @@
         <v>62</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P329" s="2" t="s">
         <v>533</v>
@@ -48644,13 +48641,13 @@
         <v>62</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P330" s="2" t="s">
         <v>533</v>
@@ -48679,13 +48676,13 @@
         <v>62</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P331" s="2" t="s">
         <v>533</v>
@@ -48714,13 +48711,13 @@
         <v>62</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P332" s="2" t="s">
         <v>533</v>
@@ -48749,13 +48746,13 @@
         <v>63</v>
       </c>
       <c r="B333" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C333" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="C333" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="D333" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AE333" s="1" t="s">
         <v>914</v>
@@ -48773,7 +48770,7 @@
         <v>57.206208425720618</v>
       </c>
       <c r="AY333" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="334" spans="1:51" ht="90" x14ac:dyDescent="0.25">
@@ -48781,13 +48778,13 @@
         <v>63</v>
       </c>
       <c r="B334" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C334" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="C334" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="D334" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AM334" s="1">
         <v>24.1</v>
@@ -48799,7 +48796,7 @@
         <v>38.589211618257259</v>
       </c>
       <c r="AY334" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="335" spans="1:51" ht="90" x14ac:dyDescent="0.25">
@@ -48807,13 +48804,13 @@
         <v>63</v>
       </c>
       <c r="B335" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="C335" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="D335" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AM335" s="1">
         <v>37.799999999999997</v>
@@ -48825,7 +48822,7 @@
         <v>43.121693121693113</v>
       </c>
       <c r="AY335" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="336" spans="1:51" ht="90" x14ac:dyDescent="0.25">
@@ -48833,13 +48830,13 @@
         <v>63</v>
       </c>
       <c r="B336" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C336" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="C336" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="D336" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AM336" s="1">
         <v>21.2</v>
@@ -48851,7 +48848,7 @@
         <v>33.96226415094339</v>
       </c>
       <c r="AY336" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>
